--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>drobné: © 2026 Universal Website</t>
+          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
@@ -1381,74 +1381,105 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Obrázky a média</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
+          <t>Proměnné</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
+          <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>proměnná</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>anglicky</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>co se dosadí</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>příklad</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>{rok}</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>{year}</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>drobné: © {rok} {web}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>{web}</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>{site}</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Název webu z listu site (site_name).</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>text: Vítejte na {web}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr"/>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Napíše se jako ©.</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>drobné: (c) {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Publikování</t>
+          <t>Obrázky a média</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1491,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
+          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1503,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
         </is>
       </c>
     </row>
@@ -1484,38 +1515,38 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Pravidla</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Publikování</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1558,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1570,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
         </is>
       </c>
     </row>
@@ -1551,90 +1582,171 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>Pravidla</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>bílé buňky</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr"/>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>šedé buňky</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Poznámky pro vás. Na webu se neobjeví.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>roletky</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B57:D57"/>
+  <mergeCells count="21">
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B78:D78"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B79:D79"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B81:D81"/>
     <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B59:D59"/>
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5973,12 +6085,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>drobné: © 2026 Universal Website · Postaveno z tabulky</t>
+          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Patička na každé stránce. Stejný zápis jako content.</t>
+          <t>Patička na každé stránce. Stejný zápis jako content. {rok} je vždy aktuální rok, {web} je site_name. Prázdné = © rok a název webu.</t>
         </is>
       </c>
     </row>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -996,12 +996,12 @@
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>steps / cards / bullets</t>
+          <t>steps / cards / bullets / faq</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>steps čísluje karty podle order; cards bez čísel</t>
+          <t>steps čísluje karty podle order; cards bez čísel; faq = rozbalovací otázky (title = otázka, text = odpověď)</t>
         </is>
       </c>
     </row>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -7068,26 +7068,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>show_folio</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>yes / no</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Zobrazit malé číslo stránky (02 / 05) nahoře.</t>
-        </is>
-      </c>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="15" t="n"/>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1381,372 +1381,675 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Proměnné</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+          <t>Barevné profily (styles › color_profile)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
+          <t>V listu styles vyberte v řádku color_profile jeden profil. Pozadí zůstává živé a jemně proměnlivé, profil mu dává základní tón. Kromě manual profily nepoužívají sloupec hue ani barvy textu z listu styles.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>proměnná</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>anglicky</t>
-        </is>
-      </c>
+          <t>profil</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr"/>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>co se dosadí</t>
+          <t>jak působí</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>příklad</t>
+          <t>barvy</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>{rok}</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>{year}</t>
-        </is>
-      </c>
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr"/>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>drobné: © {rok} {web}</t>
+          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>{web}</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>{site}</t>
-        </is>
-      </c>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>terakota</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Název webu z listu site (site_name).</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>text: Vítejte na {web}.</t>
+          <t>Jedna barva v odstínech. Teplá cihlová.</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>#C8643B</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>(c)</t>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>jantar</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Napíše se jako ©.</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>drobné: (c) {rok} {web}</t>
+          <t>Jedna barva v odstínech. Medová, zlatavá.</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>#D9932E</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>koral</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Svěží korálová.</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>#E8715A</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Obrázky a média</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>broskev</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr"/>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Jemná broskvová.</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>#E89B7A</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>karamel</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Karamelově hnědá.</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>#B9773F</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>ruze</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr"/>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Prášková růže.</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>#C97B84</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>vinova</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr"/>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Hluboká vínová.</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>#9E3B5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>pisek</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr"/>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Jedna barva v odstínech. Světlý písek.</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>#C9A77A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>tron</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr"/>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Neonově azurová s oranžovou, ubíhající mřížka v pozadí.</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>#00E5FF · #FF7A1A</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>matrix</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr"/>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Fosforově zelená, jemně padající znaky v pozadí.</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>#00FF41</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Publikování</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>soumrak</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>zeme</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr"/>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>pastel</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr"/>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>sever</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr"/>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>Čtyři barvy. Severská modrá, šalvěj, pšeničná, tlumená červená.</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>#88C0D0 #A3BE8C #EBCB8B #BF616A</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>Proměnné</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>proměnná</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>anglicky</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>co se dosadí</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>příklad</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>{rok}</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>{year}</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>drobné: © {rok} {web}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>{web}</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>{site}</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Název webu z listu site (site_name).</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>text: Vítejte na {web}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr"/>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Napíše se jako ©.</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>drobné: (c) {rok} {web}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Obrázky a média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Publikování</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
           <t>Pravidla</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>bílé buňky</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr"/>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>šedé buňky</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Poznámky pro vás. Na webu se neobjeví.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>roletky</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr"/>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B78:D78"/>
+  <mergeCells count="22">
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B87:D87"/>
     <mergeCell ref="A34:D34"/>
+    <mergeCell ref="B99:D99"/>
+    <mergeCell ref="B84:D84"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B92:D92"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="B85:D85"/>
     <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B97:D97"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B81:D81"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B96:D96"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="B86:D86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6710,160 +7013,160 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>background</t>
+          <t>color_profile</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>drift</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>drift / still / solid</t>
+          <t>roletka (viz Návod)</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>drift: barvy se pomalu pohybují. still: stejné barvy bez pohybu. solid: jedna barva.</t>
+          <t>Barevný profil webu. manual = barvy podle sloupce hue v pages a nastavení níže. Ostatní profily nastaví barvy samy.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>background_speed</t>
+          <t>background</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>drift</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>slow / normal</t>
+          <t>drift / still / solid</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Jak rychle se barvy pozadí mění.</t>
+          <t>drift: barvy se pomalu pohybují. still: stejné barvy bez pohybu. solid: jedna barva.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>background_follows_page</t>
+          <t>background_speed</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>yes / no</t>
+          <t>slow / normal</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Pozadí přebírá barvu stránky, která je vepředu.</t>
+          <t>Jak rychle se barvy pozadí mění.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>glass_opacity</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0.6</v>
+          <t>background_follows_page</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>0.3 – 0.95</t>
+          <t>yes / no</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Jak plné jsou stránky. Méně = víc pozadí prosvítá.</t>
+          <t>Pozadí přebírá barvu stránky, která je vepředu.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>page_width</t>
+          <t>glass_opacity</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>860</v>
+        <v>0.6</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>640 – 1200 (px)</t>
+          <t>0.3 – 0.95</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Největší šířka stránky na počítači.</t>
+          <t>Jak plné jsou stránky. Méně = víc pozadí prosvítá.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>page_radius</t>
+          <t>page_width</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>22</v>
+        <v>860</v>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>0 – 40 (px)</t>
+          <t>640 – 1200 (px)</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Zaoblení rohů stránky.</t>
+          <t>Největší šířka stránky na počítači.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>font_display</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Gloock</t>
-        </is>
+          <t>page_radius</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>22</v>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>libovolný Google Font</t>
+          <t>0 – 40 (px)</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Písmo nadpisů.</t>
+          <t>Zaoblení rohů stránky.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>font_body</t>
+          <t>font_display</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Figtree</t>
+          <t>Gloock</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -6873,19 +7176,19 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Písmo textu.</t>
+          <t>Písmo nadpisů.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>font_utility</t>
+          <t>font_body</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>JetBrains Mono</t>
+          <t>Figtree</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -6895,61 +7198,61 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Písmo malých popisků a čísel.</t>
+          <t>Písmo textu.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>text_size</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>16</v>
+          <t>font_utility</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>JetBrains Mono</t>
+        </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>14 – 20 (px)</t>
+          <t>libovolný Google Font</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Základní velikost textu. Nadpisy se odvodí.</t>
+          <t>Písmo malých popisků a čísel.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>text_color</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>#ECE9F4</t>
-        </is>
+          <t>text_size</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>16</v>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>hex barva</t>
+          <t>14 – 20 (px)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Hlavní barva textu.</t>
+          <t>Základní velikost textu. Nadpisy se odvodí.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>muted_color</t>
+          <t>text_color</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>#A29FB7</t>
+          <t>#ECE9F4</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -6959,117 +7262,135 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Barva popisků a vedlejšího textu.</t>
+          <t>Hlavní barva textu.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>hue_saturation</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>70</v>
+          <t>muted_color</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>#A29FB7</t>
+        </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>0 – 100</t>
+          <t>hex barva</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Jak syté jsou barvy stránek. 0 = jen šedé.</t>
+          <t>Barva popisků a vedlejšího textu.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>turn_speed</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
+          <t>hue_saturation</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>70</v>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>slow / normal / quick</t>
+          <t>0 – 100</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Rychlost otočení.</t>
+          <t>Jak syté jsou barvy stránek. 0 = jen šedé.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>turn_angle</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>30</v>
+          <t>turn_speed</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>0 – 45 (stupňů)</t>
+          <t>slow / normal / quick</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Jak moc se stoh natočí bokem. 0 natočení vypne.</t>
+          <t>Rychlost otočení.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>stack_depth</t>
+          <t>turn_angle</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>1 – 8</t>
+          <t>0 – 45 (stupňů)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Kolik stránek je při otáčení vidět za tou přední.</t>
+          <t>Jak moc se stoh natočí bokem. 0 natočení vypne.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
+          <t>stack_depth</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>1 – 8</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Kolik stránek je při otáčení vidět za tou přední.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t>tabs_desktop</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>right / left</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Na které straně jsou záložky na počítači.</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="C20" s="15" t="n"/>
@@ -7792,6 +8113,11 @@
       <c r="D199" s="15" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Neznámý profil" error="Vyberte jeden z nabízených profilů." type="list">
+      <formula1>"manual,terakota,jantar,koral,broskev,karamel,ruze,vinova,pisek,tron,matrix,soumrak,zeme,pastel,sever"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -1437,7 +1437,7 @@
       <c r="B60" s="5" t="inlineStr"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Teplá cihlová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -1455,7 +1455,7 @@
       <c r="B61" s="5" t="inlineStr"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Medová, zlatavá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="B62" s="5" t="inlineStr"/>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Svěží korálová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -1491,7 +1491,7 @@
       <c r="B63" s="5" t="inlineStr"/>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Jemná broskvová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -1509,7 +1509,7 @@
       <c r="B64" s="5" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Karamelově hnědá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -1527,7 +1527,7 @@
       <c r="B65" s="5" t="inlineStr"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Prášková růže.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -1545,7 +1545,7 @@
       <c r="B66" s="5" t="inlineStr"/>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Hluboká vínová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -1563,7 +1563,7 @@
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech. Světlý písek.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -1575,36 +1575,36 @@
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>tron</t>
+          <t>seda</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Neonově azurová s oranžovou, ubíhající mřížka v pozadí.</t>
+          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>#00E5FF · #FF7A1A</t>
+          <t>#9C9C9E</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>matrix</t>
+          <t>tron</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Fosforově zelená, jemně padající znaky v pozadí.</t>
+          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>#00FF41</t>
+          <t>#00E5FF · #FF7A1A</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Neznámý profil" error="Vyberte jeden z nabízených profilů." type="list">
-      <formula1>"manual,terakota,jantar,koral,broskev,karamel,ruze,vinova,pisek,tron,matrix,soumrak,zeme,pastel,sever"</formula1>
+      <formula1>"manual,terakota,jantar,koral,broskev,karamel,ruze,vinova,pisek,seda,tron,soumrak,zeme,pastel,sever"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Widgety, formuláře, cokoli vlastního.</t>
+          <t>Widgety a cokoli vlastního.</t>
         </is>
       </c>
     </row>
@@ -887,483 +887,505 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Jedno slovo bez mezer, které odpovídá existujícímu id, se vždy vezme jako odkaz na ten obsah. Cokoli jiného se zobrazí jako text.</t>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>formulář:</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>form:</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>kontakt (zprávy chodí na form_email z listu site)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>formulář: kontakt</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>Jedno slovo bez mezer, které odpovídá existujícímu id, se vždy vezme jako odkaz na ten obsah. Cokoli jiného se zobrazí jako text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Za svislou čáru | můžete napsat styl. Bez stylu se použije výchozí (první v tabulce níže).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>obsah</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr"/>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>styly</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>co znamenají</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr"/>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>normal / wide / centered / large</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>large = větší písmo pro výrazné sdělení</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>obrázek</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>inset / full</t>
+          <t>normal / wide / centered / large</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>full = přes celou šířku stránky</t>
+          <t>large = větší písmo pro výrazné sdělení</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>galerie</t>
+          <t>obrázek</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>grid / row</t>
+          <t>inset / full</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>row = řada, která se posouvá do strany</t>
+          <t>full = přes celou šířku stránky</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>galerie</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>normal / wide</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
+          <t>grid / row</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>row = řada, která se posouvá do strany</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>seznam</t>
+          <t>video</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
+          <t>normal / wide</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>seznam</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
           <t>steps / cards / bullets / faq</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>steps čísluje karty podle order; cards bez čísel; faq = rozbalovací otázky (title = otázka, text = odpověď)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Formátování textu</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Tato slova můžete psát přímo v content stránky i v listu texts. Vše v jedné buňce, každou část na nový řádek.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>klíčové slovo</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>anglicky</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>co vytvoří</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>úvod:</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>lead:</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Velký úvodní odstavec</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>úvod: Každá stránka se čte jako běžný web.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>text:</t>
+          <t>úvod:</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>text:</t>
+          <t>lead:</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Odstavec. Prázdný řádek uvnitř = nový odstavec.</t>
+          <t>Velký úvodní odstavec</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>text: Ostatní stránky nejsou vidět.</t>
+          <t>úvod: Každá stránka se čte jako běžný web.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>nadpis:</t>
+          <t>text:</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>heading:</t>
+          <t>text:</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Nadpis oddílu</t>
+          <t>Odstavec. Prázdný řádek uvnitř = nový odstavec.</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>nadpis: Proč je to rychlé</t>
+          <t>text: Ostatní stránky nejsou vidět.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>mezititulek:</t>
+          <t>nadpis:</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>subheading:</t>
+          <t>heading:</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Menší nadpis</t>
+          <t>Nadpis oddílu</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>mezititulek: Zkuste ho přerušit</t>
+          <t>nadpis: Proč je to rychlé</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>citace:</t>
+          <t>mezititulek:</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>quote:</t>
+          <t>subheading:</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Zvýrazněná citace</t>
+          <t>Menší nadpis</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>citace: Ať to působí jako skutečná stránka.</t>
+          <t>mezititulek: Zkuste ho přerušit</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>autor:</t>
+          <t>citace:</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>author:</t>
+          <t>quote:</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Kdo to řekl; patří k citaci nad ním</t>
+          <t>Zvýrazněná citace</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>autor: Studio</t>
+          <t>citace: Ať to působí jako skutečná stránka.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>seznam:</t>
+          <t>autor:</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>list:</t>
+          <t>author:</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Odrážky oddělené ; nebo řádky začínající -</t>
+          <t>Kdo to řekl; patří k citaci nad ním</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>seznam: rychlé; lehké; z tabulky</t>
+          <t>autor: Studio</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>poznámka:</t>
+          <t>seznam:</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>note:</t>
+          <t>list:</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Rámeček s poznámkou</t>
+          <t>Odrážky oddělené ; nebo řádky začínající -</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>poznámka: Tabulka se čte při sestavení.</t>
+          <t>seznam: rychlé; lehké; z tabulky</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>tlačítko:</t>
+          <t>poznámka:</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>button:</t>
+          <t>note:</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Tlačítko: popis -&gt; odkaz</t>
+          <t>Rámeček s poznámkou</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>tlačítko: Napište nám -&gt; https://example.com</t>
+          <t>poznámka: Tabulka se čte při sestavení.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>oddělovač:</t>
+          <t>tlačítko:</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>divider:</t>
+          <t>button:</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Tenká čára; za dvojtečkou nic</t>
+          <t>Tlačítko: popis -&gt; odkaz</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>oddělovač:</t>
+          <t>tlačítko: Napište nám -&gt; https://example.com</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
+          <t>oddělovač:</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>divider:</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Tenká čára; za dvojtečkou nic</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>oddělovač:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
           <t>drobné:</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>small:</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Drobný text</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>uvnitř textu</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr"/>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>výsledek</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>**slova**</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>tučně</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>stoh **změní směr**</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>*slova*</t>
+          <t>**slova**</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>kurzíva</t>
+          <t>tučně</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>z *Google Sheets*</t>
+          <t>stoh **změní směr**</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>[slova](odkaz)</t>
+          <t>*slova*</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr">
         <is>
+          <t>kurzíva</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>z *Google Sheets*</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>[slova](odkaz)</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
           <t>odkaz</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>viz [naše studio](https://example.com)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Celá stránka v jedné buňce</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="150" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
+    <row r="55" ht="150" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>úvod: Až bude pohyb sedět, přijde platforma pod ním.
 text: t-intro
@@ -1378,422 +1400,410 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Barevné profily (styles › color_profile)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="42" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>V listu styles vyberte v řádku color_profile jeden profil. Pozadí zůstává živé a jemně proměnlivé, profil mu dává základní tón. Kromě manual profily nepoužívají sloupec hue ani barvy textu z listu styles.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>profil</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr"/>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr"/>
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>jak působí</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>barvy</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr"/>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>terakota</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr"/>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
+          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>#C8643B</t>
+          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>jantar</t>
+          <t>terakota</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>#D9932E</t>
+          <t>#C8643B</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>koral</t>
+          <t>jantar</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr"/>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>#E8715A</t>
+          <t>#D9932E</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>broskev</t>
+          <t>koral</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr"/>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>#E89B7A</t>
+          <t>#E8715A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>karamel</t>
+          <t>broskev</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>#B9773F</t>
+          <t>#E89B7A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>ruze</t>
+          <t>karamel</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>#C97B84</t>
+          <t>#B9773F</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>vinova</t>
+          <t>ruze</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr"/>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>#9E3B5A</t>
+          <t>#C97B84</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>pisek</t>
+          <t>vinova</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>#C9A77A</t>
+          <t>#9E3B5A</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>seda</t>
+          <t>pisek</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>#9C9C9E</t>
+          <t>#C9A77A</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>tron</t>
+          <t>seda</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
+          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>#00E5FF · #FF7A1A</t>
+          <t>#9C9C9E</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>soumrak</t>
+          <t>tron</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr"/>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
+          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
+          <t>#00E5FF · #FF7A1A</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>zeme</t>
+          <t>soumrak</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
+          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
+          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>pastel</t>
+          <t>zeme</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>sever</t>
+          <t>pastel</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
       <c r="C73" s="5" t="inlineStr">
         <is>
+          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>sever</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr"/>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
           <t>Čtyři barvy. Severská modrá, šalvěj, pšeničná, tlumená červená.</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>#88C0D0 #A3BE8C #EBCB8B #BF616A</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Proměnné</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>proměnná</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>anglicky</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>co se dosadí</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>{rok}</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>{year}</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>{web}</t>
+          <t>{rok}</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>{site}</t>
+          <t>{year}</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Název webu z listu site (site_name).</t>
+          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>text: Vítejte na {web}.</t>
+          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
+          <t>{web}</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>{site}</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Název webu z listu site (site_name).</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>text: Vítejte na {web}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
           <t>(c)</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr"/>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr"/>
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>Napíše se jako ©.</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>drobné: (c) {rok} {web}</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Obrázky a média</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1815,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
+          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1827,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
+          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1839,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
         </is>
       </c>
     </row>
@@ -1841,26 +1851,26 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
+          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Publikování</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1882,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1884,26 +1894,26 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
+          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Pravidla</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1925,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1937,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1949,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1961,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
         </is>
       </c>
     </row>
@@ -1963,64 +1973,76 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="8" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr"/>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Obsah stránky a texty. Tady skládáte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>bílé buňky</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Nastavení a údaje.</t>
+          <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>šedé buňky</t>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>bílé buňky</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Poznámky pro vás. Na webu se neobjeví.</t>
+          <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>roletky</t>
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>šedé buňky</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Poznámky pro vás. Na webu se neobjeví.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>roletky</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
@@ -2029,26 +2051,26 @@
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="B98:D98"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B87:D87"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A77:D77"/>
     <mergeCell ref="B99:D99"/>
     <mergeCell ref="B84:D84"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="B92:D92"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="B95:D95"/>
     <mergeCell ref="B85:D85"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="B97:D97"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="B100:D100"/>
     <mergeCell ref="B91:D91"/>
-    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="B96:D96"/>
-    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A76:D76"/>
     <mergeCell ref="B86:D86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6398,7 +6420,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="15" t="n"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>form_email</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Kam chodí zprávy z formuláře (formulář: kontakt). Na webu se nezobrazí. Více adres oddělte čárkou.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="C11" s="15" t="n"/>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1286,106 +1286,128 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
+          <t>mezera:</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>space:</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Volné místo. Prázdné = běžná, nebo velká / malá</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>mezera: velká</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
           <t>drobné:</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>small:</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Drobný text</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>uvnitř textu</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr"/>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr"/>
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>výsledek</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>**slova**</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr"/>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>tučně</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>stoh **změní směr**</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>*slova*</t>
+          <t>**slova**</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>kurzíva</t>
+          <t>tučně</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>z *Google Sheets*</t>
+          <t>stoh **změní směr**</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>[slova](odkaz)</t>
+          <t>*slova*</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
+          <t>kurzíva</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>z *Google Sheets*</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>[slova](odkaz)</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
           <t>odkaz</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>viz [naše studio](https://example.com)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Celá stránka v jedné buňce</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="150" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="56" ht="150" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>úvod: Až bude pohyb sedět, přijde platforma pod ním.
 text: t-intro
@@ -1400,422 +1422,410 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Barevné profily (styles › color_profile)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="42" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>V listu styles vyberte v řádku color_profile jeden profil. Pozadí zůstává živé a jemně proměnlivé, profil mu dává základní tón. Kromě manual profily nepoužívají sloupec hue ani barvy textu z listu styles.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>profil</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr"/>
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>jak působí</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>barvy</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr"/>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>terakota</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr"/>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
+          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>#C8643B</t>
+          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>jantar</t>
+          <t>terakota</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr"/>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>#D9932E</t>
+          <t>#C8643B</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>koral</t>
+          <t>jantar</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr"/>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>#E8715A</t>
+          <t>#D9932E</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>broskev</t>
+          <t>koral</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>#E89B7A</t>
+          <t>#E8715A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>karamel</t>
+          <t>broskev</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>#B9773F</t>
+          <t>#E89B7A</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>ruze</t>
+          <t>karamel</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr"/>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>#C97B84</t>
+          <t>#B9773F</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>vinova</t>
+          <t>ruze</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>#9E3B5A</t>
+          <t>#C97B84</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>pisek</t>
+          <t>vinova</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>#C9A77A</t>
+          <t>#9E3B5A</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>seda</t>
+          <t>pisek</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>#9C9C9E</t>
+          <t>#C9A77A</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>tron</t>
+          <t>seda</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr"/>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
+          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>#00E5FF · #FF7A1A</t>
+          <t>#9C9C9E</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>soumrak</t>
+          <t>tron</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
+          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
+          <t>#00E5FF · #FF7A1A</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>zeme</t>
+          <t>soumrak</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
+          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
+          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>pastel</t>
+          <t>zeme</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>sever</t>
+          <t>pastel</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
       <c r="C74" s="5" t="inlineStr">
         <is>
+          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>sever</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr"/>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
           <t>Čtyři barvy. Severská modrá, šalvěj, pšeničná, tlumená červená.</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>#88C0D0 #A3BE8C #EBCB8B #BF616A</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Proměnné</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>proměnná</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>anglicky</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>co se dosadí</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>{rok}</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>{year}</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>{web}</t>
+          <t>{rok}</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>{site}</t>
+          <t>{year}</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Název webu z listu site (site_name).</t>
+          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>text: Vítejte na {web}.</t>
+          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
+          <t>{web}</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>{site}</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Název webu z listu site (site_name).</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>text: Vítejte na {web}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
           <t>(c)</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr"/>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr"/>
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>Napíše se jako ©.</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>drobné: (c) {rok} {web}</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Obrázky a média</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1837,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
+          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1849,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
+          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1861,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
         </is>
       </c>
     </row>
@@ -1863,26 +1873,26 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
+          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Publikování</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1904,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1906,26 +1916,26 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
+          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Pravidla</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1947,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1959,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1971,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1983,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
         </is>
       </c>
     </row>
@@ -1985,64 +1995,76 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="8" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr"/>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Obsah stránky a texty. Tady skládáte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>bílé buňky</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Nastavení a údaje.</t>
+          <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>šedé buňky</t>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>bílé buňky</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Poznámky pro vás. Na webu se neobjeví.</t>
+          <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>roletky</t>
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>šedé buňky</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Poznámky pro vás. Na webu se neobjeví.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>roletky</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
@@ -2055,21 +2077,21 @@
     <mergeCell ref="B101:D101"/>
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B87:D87"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A77:D77"/>
     <mergeCell ref="B99:D99"/>
-    <mergeCell ref="B84:D84"/>
     <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="B92:D92"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B94:D94"/>
     <mergeCell ref="B85:D85"/>
+    <mergeCell ref="A78:D78"/>
     <mergeCell ref="B97:D97"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="B100:D100"/>
-    <mergeCell ref="B91:D91"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="B102:D102"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="B93:D93"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="B96:D96"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B86:D86"/>
   </mergeCells>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1286,128 +1286,150 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>mezera:</t>
+          <t>mapa:</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>space:</t>
+          <t>map:</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Volné místo. Prázdné = běžná, nebo velká / malá</t>
+          <t>Mapa Google. Prázdné = adresa z listu site, nebo jiná adresa; | light = světlá</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>mezera: velká</t>
+          <t>mapa:</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>mezera:</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>space:</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Volné místo. Prázdné = běžná, nebo velká / malá</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>mezera: velká</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>drobné:</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>small:</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Drobný text</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>uvnitř textu</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr"/>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr"/>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>výsledek</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>**slova**</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>tučně</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>stoh **změní směr**</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>*slova*</t>
+          <t>**slova**</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>kurzíva</t>
+          <t>tučně</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>z *Google Sheets*</t>
+          <t>stoh **změní směr**</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>[slova](odkaz)</t>
+          <t>*slova*</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
       <c r="C53" s="5" t="inlineStr">
         <is>
+          <t>kurzíva</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>z *Google Sheets*</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>[slova](odkaz)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
           <t>odkaz</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>viz [naše studio](https://example.com)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Celá stránka v jedné buňce</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="150" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+    <row r="57" ht="150" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>úvod: Až bude pohyb sedět, přijde platforma pod ním.
 text: t-intro
@@ -1422,422 +1444,410 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Barevné profily (styles › color_profile)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>V listu styles vyberte v řádku color_profile jeden profil. Pozadí zůstává živé a jemně proměnlivé, profil mu dává základní tón. Kromě manual profily nepoužívají sloupec hue ani barvy textu z listu styles.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>profil</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr"/>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr"/>
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>jak působí</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>barvy</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr"/>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>terakota</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr"/>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
+          <t>Barvu každé stránky určuje sloupec hue v listu pages.</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>#C8643B</t>
+          <t>podle vás</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>jantar</t>
+          <t>terakota</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr"/>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Teplá cihlová.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>#D9932E</t>
+          <t>#C8643B</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>koral</t>
+          <t>jantar</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr"/>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Medová, zlatavá.</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>#E8715A</t>
+          <t>#D9932E</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>broskev</t>
+          <t>koral</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr"/>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Svěží korálová.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>#E89B7A</t>
+          <t>#E8715A</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>karamel</t>
+          <t>broskev</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr"/>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Jemná broskvová.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>#B9773F</t>
+          <t>#E89B7A</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>ruze</t>
+          <t>karamel</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr"/>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Karamelově hnědá.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>#C97B84</t>
+          <t>#B9773F</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>vinova</t>
+          <t>ruze</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr"/>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Prášková růže.</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>#9E3B5A</t>
+          <t>#C97B84</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>pisek</t>
+          <t>vinova</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr"/>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Hluboká vínová.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>#C9A77A</t>
+          <t>#9E3B5A</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>seda</t>
+          <t>pisek</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr"/>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
+          <t>Jedna barva v odstínech, pozadí v doplňkové barvě. Světlý písek.</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>#9C9C9E</t>
+          <t>#C9A77A</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>tron</t>
+          <t>seda</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr"/>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
+          <t>Stupně šedi, bez barvy. Pozadí v tmavě šedých tónech.</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>#00E5FF · #FF7A1A</t>
+          <t>#9C9C9E</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>soumrak</t>
+          <t>tron</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
+          <t>Neonově azurová s oranžovou, záře na hranách, pozadí v modrých a oranžových tónech.</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
+          <t>#00E5FF · #FF7A1A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>zeme</t>
+          <t>soumrak</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
+          <t>Čtyři barvy se střídají po stránkách. Tlumená korálová, indigo, tyrkys, zlatá.</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
+          <t>#D98B6A #7C78C8 #5BA8A0 #D9B86C</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>pastel</t>
+          <t>zeme</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+          <t>Čtyři barvy. Mech, okr, cihla, jezerní modrá.</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+          <t>#8FBF6F #E9A23B #C9583E #4F86C6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>sever</t>
+          <t>pastel</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
       <c r="C75" s="5" t="inlineStr">
         <is>
+          <t>Čtyři barvy. Tlumená růžová, aqua, levandulová, světlá citronová.</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>#D9A3B8 #9CCBCF #A3B4D9 #DCD9A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>sever</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr"/>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
           <t>Čtyři barvy. Severská modrá, šalvěj, pšeničná, tlumená červená.</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>#88C0D0 #A3BE8C #EBCB8B #BF616A</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Proměnné</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Do kteréhokoli textu můžete napsat proměnnou ve složených závorkách. Web ji při sestavení nahradí.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>proměnná</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>anglicky</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>co se dosadí</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>příklad</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>{rok}</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>{year}</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>{web}</t>
+          <t>{rok}</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>{site}</t>
+          <t>{year}</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Název webu z listu site (site_name).</t>
+          <t>Aktuální rok. Mění se sám, i když web dlouho nepublikujete.</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>text: Vítejte na {web}.</t>
+          <t>drobné: © {rok} {web}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
+          <t>{web}</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>{site}</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Název webu z listu site (site_name).</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>text: Vítejte na {web}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
           <t>(c)</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr"/>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr"/>
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>Napíše se jako ©.</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>drobné: (c) {rok} {web}</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Obrázky a média</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1859,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
+          <t>Obrázky nahrajte do složky media, která je ve složce klienta vedle této tabulky. Podsložky jsou v pořádku.</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1871,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
+          <t>V tabulce pak stačí název souboru: hero.jpg. Když je stejný název ve dvou podsložkách, napište cestu: galerie/hero.jpg.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1883,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+          <t>Web obrázky sám zmenší a převede do rychlých formátů. Nahrávejte je v plné kvalitě, nic neupravujte.</t>
         </is>
       </c>
     </row>
@@ -1885,26 +1895,26 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
+          <t>Používejte JPG, PNG nebo WebP. Fotky z iPhonu (HEIC) převeďte, nebo v iPhonu nastavte Fotoaparát → Formáty → Nejkompatibilnější.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>Videa dávejte na YouTube nebo Vimeo a do stránky vložte odkaz.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Publikování</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1926,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+          <t>Až budete s úpravami hotovi, klikněte v horním menu na Web → Publikovat. Za minutu až dvě je web online.</t>
         </is>
       </c>
     </row>
@@ -1928,26 +1938,26 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
+          <t>Výsledek se objeví v listu stav: kdy se publikovalo, jestli vše proběhlo a případná upozornění (třeba chybějící obrázek).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>Dokud nekliknete na Publikovat, návštěvníci vidí předchozí verzi. Upravovat tedy můžete v klidu.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Pravidla</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1969,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1981,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1993,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
         </is>
       </c>
     </row>
@@ -1995,7 +2005,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
         </is>
       </c>
     </row>
@@ -2007,64 +2017,76 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr"/>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Obsah stránky a texty. Tady skládáte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>bílé buňky</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Nastavení a údaje.</t>
+          <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="9" t="inlineStr">
-        <is>
-          <t>šedé buňky</t>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>bílé buňky</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Poznámky pro vás. Na webu se neobjeví.</t>
+          <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>roletky</t>
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>šedé buňky</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Poznámky pro vás. Na webu se neobjeví.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>roletky</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
@@ -2077,21 +2099,21 @@
     <mergeCell ref="B101:D101"/>
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B103:D103"/>
     <mergeCell ref="B99:D99"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="B95:D95"/>
     <mergeCell ref="B89:D89"/>
+    <mergeCell ref="A79:D79"/>
     <mergeCell ref="B94:D94"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="B97:D97"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="B100:D100"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="B90:D90"/>
     <mergeCell ref="B102:D102"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="B93:D93"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B86:D86"/>
   </mergeCells>
@@ -6455,10 +6477,34 @@
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="15" t="n"/>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Adresa pro mapu (mapa:), např. Vinohradská 12, Praha 2. Na webu se zobrazí pod mapou.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="C12" s="15" t="n"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>map_zoom</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Přiblížení mapy: 1 = celý svět, 15 = ulice, 18 = dům.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="C13" s="15" t="n"/>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1957,7 +1957,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Pravidla</t>
+          <t>Více jazyků</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
+          <t>V listu site napište do languages všechny jazyky, první je hlavní: cs, en. Hlavní jazyk je na adrese webu, další pod /en/.</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+          <t>Překlad píšete do sloupců s koncovkou jazyka vedle původních: tab_label_en, title_en, content_en, description_en v pages, content_en v texts, title_en a text_en v items, alt_en v media, html_en v embeds.</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+          <t>id_en v pages je adresa stránky v angličtině, např. why-us → /en/why-us/. Prázdné = stejné id jako v češtině.</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>Odkazy v překladu můžete psát s českým i anglickým id (/proc-s-nami/ i /why-us/), vždy povedou na anglickou verzi stránky.</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>visible_en: no skryje stránku nebo položku jen v angličtině.</t>
         </is>
       </c>
     </row>
@@ -2029,93 +2029,217 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
+          <t>Obrázky, barvy, pořadí a nastavení vzhledu jsou společné. V content_en stačí napsat stejné obrázky a galerie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Chybí-li překlad, zobrazí se původní text a v listu stav se objeví upozornění.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Návštěvník přepíná jazyk u záložek. Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>V site můžete přeložit i site_name_en, description_en a footer_en.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Pravidla</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr"/>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
         <is>
           <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>bílé buňky</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr"/>
-      <c r="C107" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
         <is>
           <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>šedé buňky</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
         <is>
           <t>Poznámky pro vás. Na webu se neobjeví.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>roletky</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr"/>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="31">
     <mergeCell ref="B98:D98"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="B101:D101"/>
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B87:D87"/>
     <mergeCell ref="B103:D103"/>
+    <mergeCell ref="B112:D112"/>
     <mergeCell ref="B99:D99"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="B95:D95"/>
     <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B104:D104"/>
     <mergeCell ref="A79:D79"/>
+    <mergeCell ref="B114:D114"/>
     <mergeCell ref="B94:D94"/>
+    <mergeCell ref="B110:D110"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="B113:D113"/>
+    <mergeCell ref="B109:D109"/>
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B102:D102"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="A57:D57"/>
+    <mergeCell ref="B105:D105"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B111:D111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6347,7 +6471,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>languages</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -6357,7 +6481,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Hlavní jazyk webu: cs nebo en. Ovlivní dělení slov a formát dat.</t>
+          <t>Jazyky webu, první je hlavní: cs, nebo cs, en. Další jazyk píšete do sloupců s koncovkou _en (viz Návod › Více jazyků).</t>
         </is>
       </c>
     </row>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -2053,7 +2053,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Návštěvník přepíná jazyk u záložek. Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
+          <t>Jazyk se dá přepnout odkazem v patičce (English / Česky). Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
         </is>
       </c>
     </row>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1957,7 +1957,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Více jazyků</t>
+          <t>Široký obsah</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>V listu site napište do languages všechny jazyky, první je hlavní: cs, en. Hlavní jazyk je na adrese webu, další pod /en/.</t>
+          <t>Když se vložený prvek (embed) nevejde na šířku stránky, třeba široká tabulka, zobrazí se na počítači jako náhled s tlačítkem Zobrazit celé. Po kliknutí se otevře celý ve vrstvě nad knihou.</t>
         </is>
       </c>
     </row>
@@ -1981,31 +1981,14 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Překlad píšete do sloupců s koncovkou jazyka vedle původních: tab_label_en, title_en, content_en, description_en v pages, content_en v texts, title_en a text_en v items, alt_en v media, html_en v embeds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>id_en v pages je adresa stránky v angličtině, např. why-us → /en/why-us/. Prázdné = stejné id jako v češtině.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Odkazy v překladu můžete psát s českým i anglickým id (/proc-s-nami/ i /why-us/), vždy povedou na anglickou verzi stránky.</t>
+          <t>Nic se nenastavuje, web to pozná sám. Na mobilu se široký obsah posouvá prstem do strany.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Více jazyků</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2000,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>visible_en: no skryje stránku nebo položku jen v angličtině.</t>
+          <t>V listu site napište do languages všechny jazyky, první je hlavní: cs, en. Hlavní jazyk je na adrese webu, další pod /en/.</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2012,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Obrázky, barvy, pořadí a nastavení vzhledu jsou společné. V content_en stačí napsat stejné obrázky a galerie.</t>
+          <t>Překlad píšete do sloupců s koncovkou jazyka vedle původních: tab_label_en, title_en, content_en, description_en v pages, content_en v texts, title_en a text_en v items, alt_en v media, html_en v embeds.</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2024,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Chybí-li překlad, zobrazí se původní text a v listu stav se objeví upozornění.</t>
+          <t>id_en v pages je adresa stránky v angličtině, např. why-us → /en/why-us/. Prázdné = stejné id jako v češtině.</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2036,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Jazyk se dá přepnout odkazem v patičce (English / Česky). Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
+          <t>Odkazy v překladu můžete psát s českým i anglickým id (/proc-s-nami/ i /why-us/), vždy povedou na anglickou verzi stránky.</t>
         </is>
       </c>
     </row>
@@ -2065,14 +2048,31 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>V site můžete přeložit i site_name_en, description_en a footer_en.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>Pravidla</t>
+          <t>visible_en: no skryje stránku nebo položku jen v angličtině.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Obrázky, barvy, pořadí a nastavení vzhledu jsou společné. V content_en stačí napsat stejné obrázky a galerie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Chybí-li překlad, zobrazí se původní text a v listu stav se objeví upozornění.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
+          <t>Jazyk se dá přepnout odkazem v patičce (English / Česky). Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
         </is>
       </c>
     </row>
@@ -2096,31 +2096,14 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>V site můžete přeložit i site_name_en, description_en a footer_en.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Pravidla</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2115,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
         </is>
       </c>
     </row>
@@ -2144,79 +2127,130 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr"/>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
         <is>
           <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>bílé buňky</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr"/>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
         <is>
           <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>šedé buňky</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr"/>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
         <is>
           <t>Poznámky pro vás. Na webu se neobjeví.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>roletky</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr"/>
-      <c r="C120" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="33">
     <mergeCell ref="B98:D98"/>
+    <mergeCell ref="B107:D107"/>
     <mergeCell ref="A35:D35"/>
-    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B117:D117"/>
     <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B116:D116"/>
     <mergeCell ref="B87:D87"/>
     <mergeCell ref="B103:D103"/>
-    <mergeCell ref="B112:D112"/>
+    <mergeCell ref="B108:D108"/>
     <mergeCell ref="B99:D99"/>
+    <mergeCell ref="B118:D118"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="B95:D95"/>
@@ -2227,19 +2261,18 @@
     <mergeCell ref="B94:D94"/>
     <mergeCell ref="B110:D110"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B100:D100"/>
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="B113:D113"/>
     <mergeCell ref="B109:D109"/>
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B115:D115"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="B105:D105"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B111:D111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/klient-sablona.xlsx
+++ b/templates/klient-sablona.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1957,7 +1957,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Široký obsah</t>
+          <t>Podstránky</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Když se vložený prvek (embed) nevejde na šířku stránky, třeba široká tabulka, zobrazí se na počítači jako náhled s tlačítkem Zobrazit celé. Po kliknutí se otevře celý ve vrstvě nad knihou.</t>
+          <t>Podstránka je řádek v pages, který má ve sloupci parent_page id hlavní stránky. Prázdné parent_page = hlavní stránka se záložkou.</t>
         </is>
       </c>
     </row>
@@ -1981,14 +1981,31 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Nic se nenastavuje, web to pozná sám. Na mobilu se široký obsah posouvá prstem do strany.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Více jazyků</t>
+          <t>Podstránky nemají vlastní záložku. Zobrazí se na listu své hlavní stránky: nejdřív obsah hlavní stránky, pak menu, pak podstránky za sebou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Menu se při čtení drží nahoře na listu a ukazuje, kde čtenář je. První položka (tab_label hlavní stránky) vede zpět nahoru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>order u podstránky určuje pořadí v rámci její hlavní stránky. tab_label je krátký název v menu, title nadpis podstránky, hue se nepoužije.</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2017,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>V listu site napište do languages všechny jazyky, první je hlavní: cs, en. Hlavní jazyk je na adrese webu, další pod /en/.</t>
+          <t>Každá podstránka má vlastní adresu, např. /jak-to-probiha/konzultace/. V odkazech stačí psát /konzultace/.</t>
         </is>
       </c>
     </row>
@@ -2012,31 +2029,14 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Překlad píšete do sloupců s koncovkou jazyka vedle původních: tab_label_en, title_en, content_en, description_en v pages, content_en v texts, title_en a text_en v items, alt_en v media, html_en v embeds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>id_en v pages je adresa stránky v angličtině, např. why-us → /en/why-us/. Prázdné = stejné id jako v češtině.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Odkazy v překladu můžete psát s českým i anglickým id (/proc-s-nami/ i /why-us/), vždy povedou na anglickou verzi stránky.</t>
+          <t>Podstránky jsou jen o jednu úroveň. Jako home_page nastavte vždy hlavní stránku.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Široký obsah</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>visible_en: no skryje stránku nebo položku jen v angličtině.</t>
+          <t>Když se vložený prvek (embed) nevejde na šířku stránky, třeba široká tabulka, zobrazí se na počítači jako náhled s tlačítkem Zobrazit celé. Po kliknutí se otevře celý ve vrstvě nad knihou.</t>
         </is>
       </c>
     </row>
@@ -2060,31 +2060,14 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Obrázky, barvy, pořadí a nastavení vzhledu jsou společné. V content_en stačí napsat stejné obrázky a galerie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Chybí-li překlad, zobrazí se původní text a v listu stav se objeví upozornění.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Jazyk se dá přepnout odkazem v patičce (English / Česky). Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
+          <t>Nic se nenastavuje, web to pozná sám. Na mobilu se široký obsah posouvá prstem do strany.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Více jazyků</t>
         </is>
       </c>
     </row>
@@ -2096,14 +2079,31 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>V site můžete přeložit i site_name_en, description_en a footer_en.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Pravidla</t>
+          <t>V listu site napište do languages všechny jazyky, první je hlavní: cs, en. Hlavní jazyk je na adrese webu, další pod /en/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Překlad píšete do sloupců s koncovkou jazyka vedle původních: tab_label_en, title_en, content_en, description_en v pages, content_en v texts, title_en a text_en v items, alt_en v media, html_en v embeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>id_en v pages je adresa stránky v angličtině, např. why-us → /en/why-us/. Prázdné = stejné id jako v češtině.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
+          <t>Odkazy v překladu můžete psát s českým i anglickým id (/proc-s-nami/ i /why-us/), vždy povedou na anglickou verzi stránky.</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+          <t>visible_en: no skryje stránku nebo položku jen v angličtině.</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+          <t>Obrázky, barvy, pořadí a nastavení vzhledu jsou společné. V content_en stačí napsat stejné obrázky a galerie.</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+          <t>Chybí-li překlad, zobrazí se původní text a v listu stav se objeví upozornění.</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+          <t>Jazyk se dá přepnout odkazem v patičce (English / Česky). Má-li prohlížeč nastavený jiný jazyk webu, otevře se mu napoprvé rovnou ten. Jeho volba se pamatuje.</t>
         </is>
       </c>
     </row>
@@ -2175,104 +2175,189 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
+          <t>V site můžete přeložit i site_name_en, description_en a footer_en.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
+          <t>Pravidla</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>id: malá písmena, bez mezer a diakritiky, slova spojená pomlčkou (t-intro, img-hero).</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>order: počítejte po desítkách (10, 20, 30). Když později něco vložíte mezi, dáte 15 a nic se nepřečísluje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>visible: no skryje stránku nebo položku, aniž byste ji mazali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Klíčové slovo s dvojtečkou vždy začíná nový kus. Nepište proto „poznámka:“ uprostřed běžné věty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Názvy sloupců (tmavé záhlaví) neměňte, web je podle nich čte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Pod patičkou každé stránky je drobný odkaz platform by filipmracek.com. Ten je součástí platformy, v tabulce se nenastavuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
           <t>Barvy v tabulce</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>žluté buňky</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr"/>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>Obsah stránky a texty. Tady skládáte.</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>bílé buňky</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr"/>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Nastavení a údaje.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>šedé buňky</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr"/>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>Poznámky pro vás. Na webu se neobjeví.</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>roletky</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr"/>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Sloupce jako visible, kind a focus berou jen nabízené hodnoty.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="39">
     <mergeCell ref="B98:D98"/>
     <mergeCell ref="B107:D107"/>
     <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B101:D101"/>
     <mergeCell ref="B117:D117"/>
     <mergeCell ref="B88:D88"/>
     <mergeCell ref="B116:D116"/>
     <mergeCell ref="B87:D87"/>
     <mergeCell ref="B103:D103"/>
-    <mergeCell ref="B108:D108"/>
+    <mergeCell ref="B112:D112"/>
     <mergeCell ref="B99:D99"/>
     <mergeCell ref="B118:D118"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A60:D60"/>
     <mergeCell ref="B95:D95"/>
     <mergeCell ref="B89:D89"/>
-    <mergeCell ref="B104:D104"/>
+    <mergeCell ref="B124:D124"/>
     <mergeCell ref="A79:D79"/>
     <mergeCell ref="B114:D114"/>
     <mergeCell ref="B94:D94"/>
     <mergeCell ref="B110:D110"/>
+    <mergeCell ref="B123:D123"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B126:D126"/>
+    <mergeCell ref="B100:D100"/>
     <mergeCell ref="B106:D106"/>
     <mergeCell ref="B113:D113"/>
-    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="B125:D125"/>
     <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B121:D121"/>
+    <mergeCell ref="B122:D122"/>
     <mergeCell ref="B102:D102"/>
     <mergeCell ref="B115:D115"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="B93:D93"/>
     <mergeCell ref="A57:D57"/>
-    <mergeCell ref="B105:D105"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B111:D111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2285,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J199"/>
+  <dimension ref="A1:K199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2298,6 +2383,7 @@
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2349,6 +2435,11 @@
       <c r="J1" s="10" t="inlineStr">
         <is>
           <t>notes</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>parent_page</t>
         </is>
       </c>
     </row>
